--- a/DateBase/orders/Nha Thu_2026-7-22.xlsx
+++ b/DateBase/orders/Nha Thu_2026-7-22.xlsx
@@ -605,6 +605,9 @@
         <v xml:space="preserve">510_翠珠白_Didiscus caeruleus 
 white_Trachymene Coerulea_1bunch</v>
       </c>
+      <c r="F21" t="str">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -663,7 +666,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01010111010101267673597756130</v>
+        <v>01010111010101267673597756132</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-7-22.xlsx
+++ b/DateBase/orders/Nha Thu_2026-7-22.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L41"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -606,12 +606,178 @@
 white_Trachymene Coerulea_1bunch</v>
       </c>
       <c r="F21" t="str">
-        <v>2</v>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>4</v>
+      </c>
+      <c r="C22" t="str">
+        <v>321_雪柳叶_Spiraea  leaves_undefined_1bunch</v>
+      </c>
+      <c r="F22" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="str">
+        <v>344_钢草_steal grass_Xanthorrhoea preissii Endl._1bunch</v>
+      </c>
+      <c r="F23" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="str">
+        <v>478_绿芯向日葵_sunflower mini_undefined_1bunch</v>
+      </c>
+      <c r="F24" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="str">
+        <v>597_尤加利叶小叶_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F25" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="str">
+        <v>316_尤加利叶大叶_Eucalyptus Cinerea_undefined_1bunch</v>
+      </c>
+      <c r="F26" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="str">
+        <v>695_百合虎皮_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F27" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="str">
+        <v>686_百合小粉仙_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F28" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="str">
+        <v>484_天鹅绒_Star of Bethlehem_undefined_1bunch</v>
+      </c>
+      <c r="F29" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="str">
+        <v>852_面包菊白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F30" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>5</v>
+      </c>
+      <c r="C31" t="str">
+        <v>316_尤加利叶大叶_Eucalyptus Cinerea_undefined_1bunch</v>
+      </c>
+      <c r="F31" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="str">
+        <v>322_喷泉草_Grasses Panicum_undefined_1bunch</v>
+      </c>
+      <c r="F32" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="str">
+        <v>453_国产菠萝_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F33" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="str">
+        <v>548_白星花_tweedia white_undefined_1bunch</v>
+      </c>
+      <c r="F34" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="str">
+        <v>221_朱丽叶塔_Julieta_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F35" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="str">
+        <v>454_蓝星花_tweedia blue_undefined_1bunch</v>
+      </c>
+      <c r="F36" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>6</v>
+      </c>
+      <c r="C37" t="str">
+        <v>653_大丽花 黑_undefined_undefined_5stems</v>
+      </c>
+      <c r="F37" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="str">
+        <v>651_大丽花 奶油桃子_undefined_undefined_5stems</v>
+      </c>
+      <c r="F38" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="str">
+        <v>668_大丽花 粉_undefined_undefined_5stems</v>
+      </c>
+      <c r="F39" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="str">
+        <v>880_铁线莲浅紫_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F40" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="str">
+        <v>790_铁线莲粉_undefined_undefined_1bunch</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -666,7 +832,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01010111010101267673597756132</v>
+        <v>010101110101012676735977561320302051055510101030515103055550</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-7-22.xlsx
+++ b/DateBase/orders/Nha Thu_2026-7-22.xlsx
@@ -774,6 +774,9 @@
       <c r="C41" t="str">
         <v>790_铁线莲粉_undefined_undefined_1bunch</v>
       </c>
+      <c r="F41" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -832,7 +835,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>010101110101012676735977561320302051055510101030515103055550</v>
+        <v>010101110101012676735977561320302051055510101030515103055555</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-7-22.xlsx
+++ b/DateBase/orders/Nha Thu_2026-7-22.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L42"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -778,9 +778,20 @@
         <v>5</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>7</v>
+      </c>
+      <c r="C42" t="str">
+        <v>470_海芋白_Calla Lily_undefined_1bunch</v>
+      </c>
+      <c r="F42" t="str">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L42"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -835,7 +846,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>010101110101012676735977561320302051055510101030515103055555</v>
+        <v>01010111010101267673597756132030205105551010103051510305555520</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-7-22.xlsx
+++ b/DateBase/orders/Nha Thu_2026-7-22.xlsx
@@ -848,6 +848,9 @@
       <c r="G2" t="str">
         <v>01010111010101267673597756132030205105551010103051510305555520</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
